--- a/data/trans_orig/IP1005-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP1005-Estudios-trans_orig.xlsx
@@ -737,7 +737,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3505</t>
+          <t>3229</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2811</t>
+          <t>3488</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4690</t>
+          <t>4158</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>87362</t>
+          <t>87638</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>84034</t>
+          <t>83357</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>173022</t>
+          <t>173554</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3390</t>
+          <t>4064</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3402</t>
+          <t>3076</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,34%</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>473601</t>
+          <t>472927</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>889676</t>
+          <t>890002</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4647</t>
+          <t>4578</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3375</t>
+          <t>3988</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>604</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5712</t>
+          <t>5159</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,55%</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>169419</t>
+          <t>169488</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>154763</t>
+          <t>154150</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>326493</t>
+          <t>327046</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>331604</t>
+          <t>331601</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5188</t>
+          <t>4664</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>602</t>
+          <t>601</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5276</t>
+          <t>5409</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1379</t>
+          <t>1375</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8855</t>
+          <t>8537</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,61%</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>675833</t>
+          <t>676357</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>716698</t>
+          <t>716565</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>721372</t>
+          <t>721373</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1394140</t>
+          <t>1394458</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1401616</t>
+          <t>1401620</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2683,7 +2683,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3476</t>
+          <t>3960</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2698,7 +2698,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2718,7 +2718,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4740</t>
+          <t>5091</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2733,7 +2733,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>673</t>
+          <t>671</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5469</t>
+          <t>5468</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>446224</t>
+          <t>445740</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>487664</t>
+          <t>487313</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>936634</t>
+          <t>936635</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>941430</t>
+          <t>941432</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3026,7 +3026,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3720</t>
+          <t>4032</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3096,7 +3096,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4063</t>
+          <t>4024</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,19%</t>
         </is>
       </c>
     </row>
@@ -3134,7 +3134,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>161620</t>
+          <t>161308</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -3149,7 +3149,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3204,7 +3204,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>332838</t>
+          <t>332877</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3364,12 +3364,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>442</t>
+          <t>437</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5273</t>
+          <t>4903</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3384,7 +3384,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3404,7 +3404,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4732</t>
+          <t>5764</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1123</t>
+          <t>1118</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7119</t>
+          <t>6906</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3454,7 +3454,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,47%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>701655</t>
+          <t>702025</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>706486</t>
+          <t>706491</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3492,7 +3492,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -3512,7 +3512,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>742769</t>
+          <t>741737</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -3527,7 +3527,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1447310</t>
+          <t>1447523</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1453306</t>
+          <t>1453311</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3562,7 +3562,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -4281,12 +4281,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>472</t>
+          <t>473</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4758</t>
+          <t>4774</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4316,12 +4316,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>675</t>
+          <t>681</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6164</t>
+          <t>6710</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4351,12 +4351,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1702</t>
+          <t>1775</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8403</t>
+          <t>7912</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,82%</t>
         </is>
       </c>
     </row>
@@ -4394,12 +4394,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>467532</t>
+          <t>467516</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>471818</t>
+          <t>471817</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4429,12 +4429,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>482571</t>
+          <t>482025</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>488060</t>
+          <t>488054</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4444,7 +4444,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4464,12 +4464,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>952622</t>
+          <t>953113</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>959323</t>
+          <t>959250</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4479,7 +4479,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4629,7 +4629,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3489</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4644,7 +4644,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4664,7 +4664,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4425</t>
+          <t>4395</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4679,7 +4679,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4694,12 +4694,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>598</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5442</t>
+          <t>5502</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4714,7 +4714,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,53%</t>
         </is>
       </c>
     </row>
@@ -4737,7 +4737,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>169214</t>
+          <t>169658</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -4752,7 +4752,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>183070</t>
+          <t>183100</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4787,7 +4787,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>354755</t>
+          <t>354695</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>359591</t>
+          <t>359599</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4967,12 +4967,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>484</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5967</t>
+          <t>5665</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4982,12 +4982,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5002,12 +5002,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1469</t>
+          <t>1383</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8101</t>
+          <t>8190</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5017,12 +5017,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5037,12 +5037,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3278</t>
+          <t>3201</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11035</t>
+          <t>11555</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5052,12 +5052,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,8%</t>
         </is>
       </c>
     </row>
@@ -5080,12 +5080,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>698404</t>
+          <t>698706</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>703767</t>
+          <t>703887</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5095,12 +5095,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,91%</t>
+          <t>99,93%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5115,12 +5115,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>736743</t>
+          <t>736654</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>743375</t>
+          <t>743461</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5130,12 +5130,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5150,12 +5150,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1438180</t>
+          <t>1437660</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1445937</t>
+          <t>1446014</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5165,12 +5165,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,77%</t>
+          <t>99,78%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP1005-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP1005-Estudios-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -727,102 +727,102 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3531</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,81%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>4,07%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
           <t>642</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3229</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3901</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,71%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>3,55%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>700</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>4,29%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>1342</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3488</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,81%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>4129</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,76%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>4,02%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1342</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>4158</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,76%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,32%</t>
         </is>
       </c>
     </row>
@@ -835,74 +835,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>86145</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>83314</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>86845</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>99,19%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>95,93%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>135</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>90225</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>87638</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>86966</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>90867</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>99,29%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>96,45%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>95,71%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>129</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>86145</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>83357</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>86845</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>99,19%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>95,98%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>264</t>
@@ -915,7 +915,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>173554</t>
+          <t>173583</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -948,57 +948,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>86845</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>86845</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>86845</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>136</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>90867</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>90867</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>90867</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>86845</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>86845</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>86845</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1065,107 +1065,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>679</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3407</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,14%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>0,71%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>679</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>4064</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,14%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>3382</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,08%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>0,85%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>679</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>3076</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,08%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,38%</t>
         </is>
       </c>
     </row>
@@ -1178,74 +1178,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>718</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>476312</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>473584</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>476991</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,86%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>99,29%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>628</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>416087</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>718</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>476312</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>472927</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>476991</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,86%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>99,15%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>1346</t>
@@ -1258,7 +1258,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>890002</t>
+          <t>889696</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1291,57 +1291,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>719</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>476991</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>476991</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>476991</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>628</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>416087</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>416087</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>416087</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>719</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>476991</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>476991</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>476991</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1408,72 +1408,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>602</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2677</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,38%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>1,69%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>1306</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4578</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>4535</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,75%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2,63%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>602</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>3988</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>600</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5159</t>
+          <t>5135</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1521,74 +1521,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>157536</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>155461</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>158138</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>99,62%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>98,31%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>252</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>172760</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>169488</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>169531</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>174066</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>99,25%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>97,37%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>97,39%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>235</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>157536</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>154150</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>158138</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>99,62%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>97,48%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>487</t>
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>327046</t>
+          <t>327070</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>331601</t>
+          <t>331605</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>158138</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>158138</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>158138</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>254</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>174066</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>174066</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>174066</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>236</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>158138</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>158138</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>158138</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1756,67 +1756,67 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>1981</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>602</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>5389</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,08%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>0,75%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
           <t>1948</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>633</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>4664</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>632</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>5742</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,29%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,09%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>0,68%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>1981</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>601</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>5409</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,08%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1375</t>
+          <t>1336</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8537</t>
+          <t>8439</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,6%</t>
         </is>
       </c>
     </row>
@@ -1864,74 +1864,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1082</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>719993</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>716585</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>721372</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,73%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>99,25%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,92%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>1015</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>679073</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>676357</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>680388</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>675279</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>680389</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>99,71%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>99,32%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>99,16%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>99,91%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1082</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>719993</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>716565</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>721373</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,73%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>99,25%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>99,92%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>2097</t>
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1394458</t>
+          <t>1394556</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1401620</t>
+          <t>1401659</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1085</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>721974</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>721974</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>721974</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>681021</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1085</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>721974</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>721974</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>721974</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2146,7 +2146,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2157,7 +2157,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2438,47 +2438,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>83537</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>133</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>91889</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>83537</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -2551,57 +2551,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>83537</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>83537</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>83537</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>133</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>91889</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>91889</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>91889</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>83537</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>83537</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>83537</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2668,72 +2668,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1351</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>4061</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>0,82%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>694</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>3960</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>4027</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,15%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>0,88%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>1351</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>5091</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>671</t>
+          <t>670</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5468</t>
+          <t>6171</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2768,7 +2768,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,66%</t>
         </is>
       </c>
     </row>
@@ -2781,74 +2781,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>703</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>491053</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>488343</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>492404</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,73%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>99,18%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>650</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>449006</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>445740</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>445673</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>449700</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>99,85%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>99,12%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>99,1%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>703</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>491053</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>487313</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>492404</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,73%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>98,97%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>1353</t>
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>936635</t>
+          <t>935932</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>941432</t>
+          <t>941433</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -2894,57 +2894,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>705</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>492404</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>492404</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>492404</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>651</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>449700</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>449700</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>449700</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>705</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>492404</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>492404</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>492404</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3011,107 +3011,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>1104</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4032</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>3801</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,67%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2,44%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>2,3%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>1104</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>3746</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,33%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>1104</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>4024</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,33%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,11%</t>
         </is>
       </c>
     </row>
@@ -3124,74 +3124,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>171561</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>232</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>164236</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>161308</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>161539</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>165340</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>99,33%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>97,56%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>97,7%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>171561</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>475</t>
@@ -3204,7 +3204,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>332877</t>
+          <t>333155</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3237,57 +3237,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>171561</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>171561</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>171561</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>234</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>165340</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>165340</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>165340</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>171561</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>171561</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>171561</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3354,72 +3354,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1351</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>4062</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>0,54%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>1797</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>437</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>4903</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>442</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>5184</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,25%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,06%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>0,69%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>1351</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>5764</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,18%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1118</t>
+          <t>1114</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6906</t>
+          <t>7101</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3454,7 +3454,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,49%</t>
         </is>
       </c>
     </row>
@@ -3467,74 +3467,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1063</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>746150</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>743439</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>747501</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,82%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>99,46%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>1015</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>705131</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>702025</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>706491</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>701744</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>706486</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>99,75%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>99,31%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>99,27%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>99,94%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1063</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>746150</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>741737</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>747501</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,82%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>99,23%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>2078</t>
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1447523</t>
+          <t>1447328</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1453311</t>
+          <t>1453315</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3562,7 +3562,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -3580,57 +3580,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>747501</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>747501</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>747501</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>706928</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>747501</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>747501</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>747501</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3749,7 +3749,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3760,7 +3760,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4041,47 +4041,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>59378</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -4154,57 +4154,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>59378</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>59378</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>59378</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4271,72 +4271,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2491</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>680</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>6031</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,51%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,14%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1,23%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>1715</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>473</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>4774</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>474</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>4922</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,36%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,1%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>1,01%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>2491</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>681</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>6710</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,51%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,14%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4351,12 +4351,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1775</t>
+          <t>1744</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7912</t>
+          <t>8386</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,87%</t>
         </is>
       </c>
     </row>
@@ -4384,74 +4384,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>691</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>486244</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>482704</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>488055</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,49%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>98,77%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,86%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>711</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>470575</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>467516</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>471817</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>467368</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>471816</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>99,64%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>98,99%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>98,96%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>99,9%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>691</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>486244</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>482025</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>488054</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,49%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>98,63%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>99,86%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>1402</t>
@@ -4464,12 +4464,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>953113</t>
+          <t>952639</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>959250</t>
+          <t>959281</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4479,7 +4479,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4497,57 +4497,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>695</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>488735</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>488735</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>488735</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>714</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>472290</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>472290</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>472290</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>695</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>488735</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>488735</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>488735</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4614,74 +4614,74 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1381</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>4398</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,74%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2,35%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>604</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3045</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>3041</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,35%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>1,76%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>1381</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>4395</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,74%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>2,34%</t>
-        </is>
-      </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>3</t>
@@ -4694,12 +4694,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>598</t>
+          <t>605</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5502</t>
+          <t>5476</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4714,7 +4714,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,52%</t>
         </is>
       </c>
     </row>
@@ -4727,74 +4727,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>269</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>186114</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>183097</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>187495</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>99,26%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>97,65%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>257</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>172099</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>169658</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>169662</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>172703</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>99,65%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>98,24%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>269</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>186114</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>183100</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>187495</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>99,26%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>97,66%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>526</t>
@@ -4807,12 +4807,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>354695</t>
+          <t>354721</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>359599</t>
+          <t>359592</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4840,57 +4840,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>271</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>187495</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>187495</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>187495</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>258</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>172703</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>172703</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>172703</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>271</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>187495</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>187495</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>187495</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4957,72 +4957,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>3872</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1359</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>8470</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,52%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1,14%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>2319</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>484</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>5665</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>605</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>5496</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,33%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,07%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>0,8%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>3872</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>1383</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>8190</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,52%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5037,12 +5037,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3201</t>
+          <t>3054</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11555</t>
+          <t>10897</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5052,12 +5052,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,75%</t>
         </is>
       </c>
     </row>
@@ -5070,72 +5070,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1059</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>740972</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>736374</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>743485</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,48%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>98,86%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,82%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>1057</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>702052</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>698706</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>703887</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>698875</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>703766</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>99,67%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>99,2%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>99,93%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1059</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>740972</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>736654</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>743461</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,48%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,81%</t>
+          <t>99,91%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5150,12 +5150,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1437660</t>
+          <t>1438318</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1446014</t>
+          <t>1446161</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5165,12 +5165,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,79%</t>
         </is>
       </c>
     </row>
@@ -5183,57 +5183,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>1061</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>704371</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
